--- a/yolo-seg__ANN/預測結果與評估指標_kfold_26n_mask幾何_長邊正規化_seed2.xlsx
+++ b/yolo-seg__ANN/預測結果與評估指標_kfold_26n_mask幾何_長邊正規化_seed2.xlsx
@@ -483,28 +483,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>757.57460000000003</v>
+        <v>610.42669999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.084452901670197</v>
+        <v>19.811310064583243</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.9155470983298031</v>
+        <v>-3.1886899354167575</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9155470983298031</v>
+        <v>3.1886899354167575</v>
       </c>
       <c r="H2" s="0">
-        <v>20.584452901670197</v>
+        <v>19.311310064583243</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.4155470983298031</v>
+        <v>-3.6886899354167575</v>
       </c>
       <c r="J2" s="0">
-        <v>2.4155470983298031</v>
+        <v>3.6886899354167575</v>
       </c>
       <c r="K2" s="0">
         <v>5</v>
@@ -524,28 +524,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>491.95310000000001</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.207797595192606</v>
+        <v>20.169890279747865</v>
       </c>
       <c r="F3" s="0">
-        <v>0.20779759519260566</v>
+        <v>-0.83010972025213547</v>
       </c>
       <c r="G3" s="0">
-        <v>0.20779759519260566</v>
+        <v>0.83010972025213547</v>
       </c>
       <c r="H3" s="0">
-        <v>20.707797595192606</v>
+        <v>19.669890279747865</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.29220240480739435</v>
+        <v>-1.3301097202521355</v>
       </c>
       <c r="J3" s="0">
-        <v>0.29220240480739435</v>
+        <v>1.3301097202521355</v>
       </c>
       <c r="K3" s="0">
         <v>2</v>
@@ -565,28 +565,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>491.89060000000001</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.095715749032767</v>
+        <v>23.246304318645024</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4042842509672333</v>
+        <v>-0.25369568135497644</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4042842509672333</v>
+        <v>0.25369568135497644</v>
       </c>
       <c r="H4" s="0">
-        <v>20.595715749032767</v>
+        <v>22.746304318645024</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9042842509672333</v>
+        <v>-0.75369568135497644</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9042842509672333</v>
+        <v>0.75369568135497644</v>
       </c>
       <c r="K4" s="0">
         <v>4</v>
@@ -606,28 +606,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>491.41719999999998</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>21.336654907871239</v>
+        <v>19.628235466402099</v>
       </c>
       <c r="F5" s="0">
-        <v>0.33665490787123886</v>
+        <v>-1.3717645335979007</v>
       </c>
       <c r="G5" s="0">
-        <v>0.33665490787123886</v>
+        <v>1.3717645335979007</v>
       </c>
       <c r="H5" s="0">
-        <v>20.836654907871239</v>
+        <v>19.128235466402099</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.16334509212876114</v>
+        <v>-1.8717645335979007</v>
       </c>
       <c r="J5" s="0">
-        <v>0.16334509212876114</v>
+        <v>1.8717645335979007</v>
       </c>
       <c r="K5" s="0">
         <v>5</v>
@@ -647,28 +647,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>505.68939999999998</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.20783404134966</v>
+        <v>20.398898630456081</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.29216595865034023</v>
+        <v>-1.1011013695439189</v>
       </c>
       <c r="G6" s="0">
-        <v>0.29216595865034023</v>
+        <v>1.1011013695439189</v>
       </c>
       <c r="H6" s="0">
-        <v>20.70783404134966</v>
+        <v>19.898898630456081</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.79216595865034023</v>
+        <v>-1.6011013695439189</v>
       </c>
       <c r="J6" s="0">
-        <v>0.79216595865034023</v>
+        <v>1.6011013695439189</v>
       </c>
       <c r="K6" s="0">
         <v>2</v>
@@ -688,28 +688,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>494.42829999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.333274395953861</v>
+        <v>22.279770034521512</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.6667256040461389</v>
+        <v>0.27977003452151195</v>
       </c>
       <c r="G7" s="0">
-        <v>0.6667256040461389</v>
+        <v>0.27977003452151195</v>
       </c>
       <c r="H7" s="0">
-        <v>20.833274395953861</v>
+        <v>21.779770034521512</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.1667256040461389</v>
+        <v>-0.22022996547848806</v>
       </c>
       <c r="J7" s="0">
-        <v>1.1667256040461389</v>
+        <v>0.22022996547848806</v>
       </c>
       <c r="K7" s="0">
         <v>5</v>
@@ -729,28 +729,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>513.30700000000002</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.243902619403336</v>
+        <v>23.851740851255773</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.756097380596664</v>
+        <v>-1.1482591487442271</v>
       </c>
       <c r="G8" s="0">
-        <v>3.756097380596664</v>
+        <v>1.1482591487442271</v>
       </c>
       <c r="H8" s="0">
-        <v>20.743902619403336</v>
+        <v>23.351740851255773</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.256097380596664</v>
+        <v>-1.6482591487442271</v>
       </c>
       <c r="J8" s="0">
-        <v>4.256097380596664</v>
+        <v>1.6482591487442271</v>
       </c>
       <c r="K8" s="0">
         <v>1</v>
@@ -770,28 +770,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>762.40570000000002</v>
+        <v>584.5915</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.208515185978776</v>
+        <v>19.771966263909132</v>
       </c>
       <c r="F9" s="0">
-        <v>0.70851518597877572</v>
+        <v>-0.72803373609086819</v>
       </c>
       <c r="G9" s="0">
-        <v>0.70851518597877572</v>
+        <v>0.72803373609086819</v>
       </c>
       <c r="H9" s="0">
-        <v>20.708515185978776</v>
+        <v>19.271966263909132</v>
       </c>
       <c r="I9" s="0">
-        <v>0.20851518597877572</v>
+        <v>-1.2280337360908682</v>
       </c>
       <c r="J9" s="0">
-        <v>0.20851518597877572</v>
+        <v>1.2280337360908682</v>
       </c>
       <c r="K9" s="0">
         <v>2</v>
@@ -811,28 +811,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>253.237</v>
+        <v>648.39279999999997</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.207164252099552</v>
+        <v>20.692282209268896</v>
       </c>
       <c r="F10" s="0">
-        <v>0.20716425209955247</v>
+        <v>-0.30771779073110395</v>
       </c>
       <c r="G10" s="0">
-        <v>0.20716425209955247</v>
+        <v>0.30771779073110395</v>
       </c>
       <c r="H10" s="0">
-        <v>20.707164252099552</v>
+        <v>20.192282209268896</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.29283574790044753</v>
+        <v>-0.80771779073110395</v>
       </c>
       <c r="J10" s="0">
-        <v>0.29283574790044753</v>
+        <v>0.80771779073110395</v>
       </c>
       <c r="K10" s="0">
         <v>2</v>
@@ -852,28 +852,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>705.75559999999996</v>
+        <v>466.6764</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.96618130715126</v>
+        <v>19.937209597451748</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9661813071512597</v>
+        <v>1.9372095974517478</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9661813071512597</v>
+        <v>1.9372095974517478</v>
       </c>
       <c r="H11" s="0">
-        <v>20.46618130715126</v>
+        <v>19.437209597451748</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4661813071512597</v>
+        <v>1.4372095974517478</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4661813071512597</v>
+        <v>1.4372095974517478</v>
       </c>
       <c r="K11" s="0">
         <v>5</v>
@@ -893,28 +893,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>493.79079999999999</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.93131682247639</v>
+        <v>23.367897297075629</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.0686831775236101</v>
+        <v>-1.6321027029243709</v>
       </c>
       <c r="G12" s="0">
-        <v>4.0686831775236101</v>
+        <v>1.6321027029243709</v>
       </c>
       <c r="H12" s="0">
-        <v>20.43131682247639</v>
+        <v>22.867897297075629</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.5686831775236101</v>
+        <v>-2.1321027029243709</v>
       </c>
       <c r="J12" s="0">
-        <v>4.5686831775236101</v>
+        <v>2.1321027029243709</v>
       </c>
       <c r="K12" s="0">
         <v>3</v>
@@ -934,28 +934,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>500.21780000000001</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.931335820592739</v>
+        <v>21.025673895349097</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.5686641794072607</v>
+        <v>-1.4743261046509026</v>
       </c>
       <c r="G13" s="0">
-        <v>1.5686641794072607</v>
+        <v>1.4743261046509026</v>
       </c>
       <c r="H13" s="0">
-        <v>20.431335820592739</v>
+        <v>20.525673895349097</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.0686641794072607</v>
+        <v>-1.9743261046509026</v>
       </c>
       <c r="J13" s="0">
-        <v>2.0686641794072607</v>
+        <v>1.9743261046509026</v>
       </c>
       <c r="K13" s="0">
         <v>3</v>
@@ -975,28 +975,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>497.86020000000002</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.119002845892812</v>
+        <v>21.525466052432464</v>
       </c>
       <c r="F14" s="0">
-        <v>0.61900284589281185</v>
+        <v>1.0254660524324635</v>
       </c>
       <c r="G14" s="0">
-        <v>0.61900284589281185</v>
+        <v>1.0254660524324635</v>
       </c>
       <c r="H14" s="0">
-        <v>20.619002845892812</v>
+        <v>21.025466052432464</v>
       </c>
       <c r="I14" s="0">
-        <v>0.11900284589281185</v>
+        <v>0.52546605243246347</v>
       </c>
       <c r="J14" s="0">
-        <v>0.11900284589281185</v>
+        <v>0.52546605243246347</v>
       </c>
       <c r="K14" s="0">
         <v>4</v>
@@ -1016,28 +1016,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>494.16919999999999</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.931317941021146</v>
+        <v>19.727925167909863</v>
       </c>
       <c r="F15" s="0">
-        <v>1.4313179410211454</v>
+        <v>0.22792516790986284</v>
       </c>
       <c r="G15" s="0">
-        <v>1.4313179410211454</v>
+        <v>0.22792516790986284</v>
       </c>
       <c r="H15" s="0">
-        <v>20.431317941021146</v>
+        <v>19.227925167909863</v>
       </c>
       <c r="I15" s="0">
-        <v>0.9313179410211454</v>
+        <v>-0.27207483209013716</v>
       </c>
       <c r="J15" s="0">
-        <v>0.9313179410211454</v>
+        <v>0.27207483209013716</v>
       </c>
       <c r="K15" s="0">
         <v>3</v>
@@ -1057,28 +1057,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>481.47469999999999</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.207769793227968</v>
+        <v>20.26027808340892</v>
       </c>
       <c r="F16" s="0">
-        <v>1.7077697932279676</v>
+        <v>0.76027808340892022</v>
       </c>
       <c r="G16" s="0">
-        <v>1.7077697932279676</v>
+        <v>0.76027808340892022</v>
       </c>
       <c r="H16" s="0">
-        <v>20.707769793227968</v>
+        <v>19.76027808340892</v>
       </c>
       <c r="I16" s="0">
-        <v>1.2077697932279676</v>
+        <v>0.26027808340892022</v>
       </c>
       <c r="J16" s="0">
-        <v>1.2077697932279676</v>
+        <v>0.26027808340892022</v>
       </c>
       <c r="K16" s="0">
         <v>2</v>
@@ -1098,28 +1098,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>247.03380000000001</v>
+        <v>564.40920000000006</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>20.799763160627943</v>
+        <v>19.54899489717241</v>
       </c>
       <c r="F17" s="0">
-        <v>2.2997631606279434</v>
+        <v>1.0489948971724097</v>
       </c>
       <c r="G17" s="0">
-        <v>2.2997631606279434</v>
+        <v>1.0489948971724097</v>
       </c>
       <c r="H17" s="0">
-        <v>20.299763160627943</v>
+        <v>19.04899489717241</v>
       </c>
       <c r="I17" s="0">
-        <v>1.7997631606279434</v>
+        <v>0.54899489717240968</v>
       </c>
       <c r="J17" s="0">
-        <v>1.7997631606279434</v>
+        <v>0.54899489717240968</v>
       </c>
       <c r="K17" s="0">
         <v>4</v>
@@ -1139,28 +1139,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>250.61840000000001</v>
+        <v>736.66660000000002</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.930598009295657</v>
+        <v>23.058903648884012</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.8194019907043426</v>
+        <v>-0.69109635111598777</v>
       </c>
       <c r="G18" s="0">
-        <v>2.8194019907043426</v>
+        <v>0.69109635111598777</v>
       </c>
       <c r="H18" s="0">
-        <v>20.430598009295657</v>
+        <v>22.558903648884012</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.3194019907043426</v>
+        <v>-1.1910963511159878</v>
       </c>
       <c r="J18" s="0">
-        <v>3.3194019907043426</v>
+        <v>1.1910963511159878</v>
       </c>
       <c r="K18" s="0">
         <v>3</v>
@@ -1180,28 +1180,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>503.90179999999998</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.251077206158193</v>
+        <v>21.134172034787103</v>
       </c>
       <c r="F19" s="0">
-        <v>-0.99892279384180682</v>
+        <v>-1.1158279652128975</v>
       </c>
       <c r="G19" s="0">
-        <v>0.99892279384180682</v>
+        <v>1.1158279652128975</v>
       </c>
       <c r="H19" s="0">
-        <v>20.751077206158193</v>
+        <v>20.634172034787103</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.4989227938418068</v>
+        <v>-1.6158279652128975</v>
       </c>
       <c r="J19" s="0">
-        <v>1.4989227938418068</v>
+        <v>1.6158279652128975</v>
       </c>
       <c r="K19" s="0">
         <v>1</v>
@@ -1221,28 +1221,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>504.19889999999998</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.320005228385032</v>
+        <v>23.554634926218782</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.1799947716149681</v>
+        <v>-1.9453650737812183</v>
       </c>
       <c r="G20" s="0">
-        <v>4.1799947716149681</v>
+        <v>1.9453650737812183</v>
       </c>
       <c r="H20" s="0">
-        <v>20.820005228385032</v>
+        <v>23.054634926218782</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.6799947716149681</v>
+        <v>-2.4453650737812183</v>
       </c>
       <c r="J20" s="0">
-        <v>4.6799947716149681</v>
+        <v>2.4453650737812183</v>
       </c>
       <c r="K20" s="0">
         <v>5</v>
@@ -1262,28 +1262,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>750.87540000000001</v>
+        <v>533.39049999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.932076760630679</v>
+        <v>19.079846070791049</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.5679232393693212</v>
+        <v>-3.4201539292089507</v>
       </c>
       <c r="G21" s="0">
-        <v>1.5679232393693212</v>
+        <v>3.4201539292089507</v>
       </c>
       <c r="H21" s="0">
-        <v>20.432076760630679</v>
+        <v>18.579846070791049</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.0679232393693212</v>
+        <v>-3.9201539292089507</v>
       </c>
       <c r="J21" s="0">
-        <v>2.0679232393693212</v>
+        <v>3.9201539292089507</v>
       </c>
       <c r="K21" s="0">
         <v>3</v>
@@ -1303,28 +1303,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>507.5804</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>21.15620901992634</v>
+        <v>20.255639734866339</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.34379098007365983</v>
+        <v>-1.2443602651336612</v>
       </c>
       <c r="G22" s="0">
-        <v>0.34379098007365983</v>
+        <v>1.2443602651336612</v>
       </c>
       <c r="H22" s="0">
-        <v>20.65620901992634</v>
+        <v>19.755639734866339</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.84379098007365982</v>
+        <v>-1.7443602651336612</v>
       </c>
       <c r="J22" s="0">
-        <v>0.84379098007365982</v>
+        <v>1.7443602651336612</v>
       </c>
       <c r="K22" s="0">
         <v>4</v>
@@ -1344,28 +1344,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>498.38549999999998</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.12103854651042</v>
+        <v>21.233486511666182</v>
       </c>
       <c r="F23" s="0">
-        <v>1.1210385465104196</v>
+        <v>1.2334865116661824</v>
       </c>
       <c r="G23" s="0">
-        <v>1.1210385465104196</v>
+        <v>1.2334865116661824</v>
       </c>
       <c r="H23" s="0">
-        <v>20.62103854651042</v>
+        <v>20.733486511666182</v>
       </c>
       <c r="I23" s="0">
-        <v>0.62103854651041957</v>
+        <v>0.7334865116661824</v>
       </c>
       <c r="J23" s="0">
-        <v>0.62103854651041957</v>
+        <v>0.7334865116661824</v>
       </c>
       <c r="K23" s="0">
         <v>4</v>
@@ -1385,28 +1385,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>487.82440000000003</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.207786640650156</v>
+        <v>19.766942052861271</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7077866406501556</v>
+        <v>0.26694205286127115</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7077866406501556</v>
+        <v>0.26694205286127115</v>
       </c>
       <c r="H24" s="0">
-        <v>20.707786640650156</v>
+        <v>19.266942052861271</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2077866406501556</v>
+        <v>-0.23305794713872885</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2077866406501556</v>
+        <v>0.23305794713872885</v>
       </c>
       <c r="K24" s="0">
         <v>2</v>
@@ -1426,28 +1426,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>497.21030000000002</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.255358528950016</v>
+        <v>19.84045531979994</v>
       </c>
       <c r="F25" s="0">
-        <v>2.7553585289500155</v>
+        <v>1.3404553197999398</v>
       </c>
       <c r="G25" s="0">
-        <v>2.7553585289500155</v>
+        <v>1.3404553197999398</v>
       </c>
       <c r="H25" s="0">
-        <v>20.755358528950016</v>
+        <v>19.34045531979994</v>
       </c>
       <c r="I25" s="0">
-        <v>2.2553585289500155</v>
+        <v>0.84045531979993982</v>
       </c>
       <c r="J25" s="0">
-        <v>2.2553585289500155</v>
+        <v>0.84045531979993982</v>
       </c>
       <c r="K25" s="0">
         <v>1</v>
@@ -1467,28 +1467,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>501.99489999999997</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.931341073673977</v>
+        <v>21.882533474650465</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.31865892632602311</v>
+        <v>0.63253347465046517</v>
       </c>
       <c r="G26" s="0">
-        <v>0.31865892632602311</v>
+        <v>0.63253347465046517</v>
       </c>
       <c r="H26" s="0">
-        <v>20.431341073673977</v>
+        <v>21.382533474650465</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.81865892632602311</v>
+        <v>0.13253347465046517</v>
       </c>
       <c r="J26" s="0">
-        <v>0.81865892632602311</v>
+        <v>0.13253347465046517</v>
       </c>
       <c r="K26" s="0">
         <v>3</v>
@@ -1508,28 +1508,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>494.10910000000001</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.104399995692649</v>
+        <v>20.756847316770507</v>
       </c>
       <c r="F27" s="0">
-        <v>1.8543999956926491</v>
+        <v>1.5068473167705072</v>
       </c>
       <c r="G27" s="0">
-        <v>1.8543999956926491</v>
+        <v>1.5068473167705072</v>
       </c>
       <c r="H27" s="0">
-        <v>20.604399995692649</v>
+        <v>20.256847316770507</v>
       </c>
       <c r="I27" s="0">
-        <v>1.3543999956926491</v>
+        <v>1.0068473167705072</v>
       </c>
       <c r="J27" s="0">
-        <v>1.3543999956926491</v>
+        <v>1.0068473167705072</v>
       </c>
       <c r="K27" s="0">
         <v>4</v>
@@ -1549,28 +1549,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>511.18400000000003</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>21.308450743622974</v>
+        <v>22.033254719634204</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.44154925637702647</v>
+        <v>0.28325471963420412</v>
       </c>
       <c r="G28" s="0">
-        <v>0.44154925637702647</v>
+        <v>0.28325471963420412</v>
       </c>
       <c r="H28" s="0">
-        <v>20.808450743622974</v>
+        <v>21.533254719634204</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.94154925637702647</v>
+        <v>-0.21674528036579588</v>
       </c>
       <c r="J28" s="0">
-        <v>0.94154925637702647</v>
+        <v>0.21674528036579588</v>
       </c>
       <c r="K28" s="0">
         <v>5</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>734.76130000000001</v>
+        <v>527.93060000000003</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.474987246917227</v>
+        <v>19.206828557347198</v>
       </c>
       <c r="F29" s="0">
-        <v>0.72498724691722671</v>
+        <v>-1.5431714426528025</v>
       </c>
       <c r="G29" s="0">
-        <v>0.72498724691722671</v>
+        <v>1.5431714426528025</v>
       </c>
       <c r="H29" s="0">
-        <v>20.974987246917227</v>
+        <v>18.706828557347198</v>
       </c>
       <c r="I29" s="0">
-        <v>0.22498724691722671</v>
+        <v>-2.0431714426528025</v>
       </c>
       <c r="J29" s="0">
-        <v>0.22498724691722671</v>
+        <v>2.0431714426528025</v>
       </c>
       <c r="K29" s="0">
         <v>4</v>
@@ -1631,28 +1631,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>502.2962</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.207825038250725</v>
+        <v>21.756593539975018</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.29217496174927504</v>
+        <v>0.2565935399750181</v>
       </c>
       <c r="G30" s="0">
-        <v>0.29217496174927504</v>
+        <v>0.2565935399750181</v>
       </c>
       <c r="H30" s="0">
-        <v>20.707825038250725</v>
+        <v>21.256593539975018</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.79217496174927504</v>
+        <v>-0.2434064600249819</v>
       </c>
       <c r="J30" s="0">
-        <v>0.79217496174927504</v>
+        <v>0.2434064600249819</v>
       </c>
       <c r="K30" s="0">
         <v>2</v>
@@ -1672,28 +1672,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>256.38499999999999</v>
+        <v>687.38679999999999</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.207172603502961</v>
+        <v>21.707005586271581</v>
       </c>
       <c r="F31" s="0">
-        <v>1.7071726035029613</v>
+        <v>2.2070055862715812</v>
       </c>
       <c r="G31" s="0">
-        <v>1.7071726035029613</v>
+        <v>2.2070055862715812</v>
       </c>
       <c r="H31" s="0">
-        <v>20.707172603502961</v>
+        <v>21.207005586271581</v>
       </c>
       <c r="I31" s="0">
-        <v>1.2071726035029613</v>
+        <v>1.7070055862715812</v>
       </c>
       <c r="J31" s="0">
-        <v>1.2071726035029613</v>
+        <v>1.7070055862715812</v>
       </c>
       <c r="K31" s="0">
         <v>2</v>
@@ -1713,28 +1713,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>252.7089</v>
+        <v>664.20730000000003</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.207162851092718</v>
+        <v>21.055870945864378</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7071628510927184</v>
+        <v>1.5558709458643776</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7071628510927184</v>
+        <v>1.5558709458643776</v>
       </c>
       <c r="H32" s="0">
-        <v>20.707162851092718</v>
+        <v>20.555870945864378</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2071628510927184</v>
+        <v>1.0558709458643776</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2071628510927184</v>
+        <v>1.0558709458643776</v>
       </c>
       <c r="K32" s="0">
         <v>2</v>
@@ -1754,28 +1754,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>251.91499999999999</v>
+        <v>700.82140000000004</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>20.602906381082271</v>
+        <v>21.777900083906982</v>
       </c>
       <c r="F33" s="0">
-        <v>-0.39709361891772943</v>
+        <v>0.77790008390698162</v>
       </c>
       <c r="G33" s="0">
-        <v>0.39709361891772943</v>
+        <v>0.77790008390698162</v>
       </c>
       <c r="H33" s="0">
-        <v>20.102906381082271</v>
+        <v>21.277900083906982</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.89709361891772943</v>
+        <v>0.27790008390698162</v>
       </c>
       <c r="J33" s="0">
-        <v>0.89709361891772943</v>
+        <v>0.27790008390698162</v>
       </c>
       <c r="K33" s="0">
         <v>1</v>
@@ -1795,28 +1795,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>499.10570000000001</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.931332533241655</v>
+        <v>19.971990734739151</v>
       </c>
       <c r="F34" s="0">
-        <v>0.68133253324165466</v>
+        <v>-0.27800926526084879</v>
       </c>
       <c r="G34" s="0">
-        <v>0.68133253324165466</v>
+        <v>0.27800926526084879</v>
       </c>
       <c r="H34" s="0">
-        <v>20.431332533241655</v>
+        <v>19.471990734739151</v>
       </c>
       <c r="I34" s="0">
-        <v>0.18133253324165466</v>
+        <v>-0.77800926526084879</v>
       </c>
       <c r="J34" s="0">
-        <v>0.18133253324165466</v>
+        <v>0.77800926526084879</v>
       </c>
       <c r="K34" s="0">
         <v>3</v>
@@ -1836,28 +1836,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>500.55090000000001</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.253311674623849</v>
+        <v>20.176862184813786</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.2466883253761516</v>
+        <v>-1.3231378151862145</v>
       </c>
       <c r="G35" s="0">
-        <v>0.2466883253761516</v>
+        <v>1.3231378151862145</v>
       </c>
       <c r="H35" s="0">
-        <v>20.753311674623849</v>
+        <v>19.676862184813786</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.7466883253761516</v>
+        <v>-1.8231378151862145</v>
       </c>
       <c r="J35" s="0">
-        <v>0.7466883253761516</v>
+        <v>1.8231378151862145</v>
       </c>
       <c r="K35" s="0">
         <v>1</v>
@@ -1877,28 +1877,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>492.50330000000002</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.257921398522932</v>
+        <v>19.939926237649182</v>
       </c>
       <c r="F36" s="0">
-        <v>1.7579213985229316</v>
+        <v>0.43992623764918193</v>
       </c>
       <c r="G36" s="0">
-        <v>1.7579213985229316</v>
+        <v>0.43992623764918193</v>
       </c>
       <c r="H36" s="0">
-        <v>20.757921398522932</v>
+        <v>19.439926237649182</v>
       </c>
       <c r="I36" s="0">
-        <v>1.2579213985229316</v>
+        <v>-0.060073762350818072</v>
       </c>
       <c r="J36" s="0">
-        <v>1.2579213985229316</v>
+        <v>0.060073762350818072</v>
       </c>
       <c r="K36" s="0">
         <v>1</v>
@@ -1918,28 +1918,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>493.493</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.101991502046371</v>
+        <v>22.819321994016495</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.8980084979536294</v>
+        <v>-2.1806780059835056</v>
       </c>
       <c r="G37" s="0">
-        <v>3.8980084979536294</v>
+        <v>2.1806780059835056</v>
       </c>
       <c r="H37" s="0">
-        <v>20.601991502046371</v>
+        <v>22.319321994016495</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.3980084979536294</v>
+        <v>-2.6806780059835056</v>
       </c>
       <c r="J37" s="0">
-        <v>4.3980084979536294</v>
+        <v>2.6806780059835056</v>
       </c>
       <c r="K37" s="0">
         <v>4</v>
@@ -1959,28 +1959,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>497.25240000000002</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>21.329796584889877</v>
+        <v>19.691490872558351</v>
       </c>
       <c r="F38" s="0">
-        <v>2.329796584889877</v>
+        <v>0.69149087255835085</v>
       </c>
       <c r="G38" s="0">
-        <v>2.329796584889877</v>
+        <v>0.69149087255835085</v>
       </c>
       <c r="H38" s="0">
-        <v>20.829796584889877</v>
+        <v>19.191490872558351</v>
       </c>
       <c r="I38" s="0">
-        <v>1.829796584889877</v>
+        <v>0.19149087255835085</v>
       </c>
       <c r="J38" s="0">
-        <v>1.829796584889877</v>
+        <v>0.19149087255835085</v>
       </c>
       <c r="K38" s="0">
         <v>5</v>
@@ -2000,28 +2000,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>507.44290000000001</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.931357177881374</v>
+        <v>22.006536419025565</v>
       </c>
       <c r="F39" s="0">
-        <v>1.9313571778813738</v>
+        <v>3.006536419025565</v>
       </c>
       <c r="G39" s="0">
-        <v>1.9313571778813738</v>
+        <v>3.006536419025565</v>
       </c>
       <c r="H39" s="0">
-        <v>20.431357177881374</v>
+        <v>21.506536419025565</v>
       </c>
       <c r="I39" s="0">
-        <v>1.4313571778813739</v>
+        <v>2.506536419025565</v>
       </c>
       <c r="J39" s="0">
-        <v>1.4313571778813739</v>
+        <v>2.506536419025565</v>
       </c>
       <c r="K39" s="0">
         <v>3</v>
@@ -2041,28 +2041,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>330.94639999999998</v>
+        <v>762.38530000000003</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.207370415025803</v>
+        <v>24.539626086625837</v>
       </c>
       <c r="F40" s="0">
-        <v>0.20737041502580311</v>
+        <v>3.5396260866258373</v>
       </c>
       <c r="G40" s="0">
-        <v>0.20737041502580311</v>
+        <v>3.5396260866258373</v>
       </c>
       <c r="H40" s="0">
-        <v>20.707370415025803</v>
+        <v>24.039626086625837</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.29262958497419689</v>
+        <v>3.0396260866258373</v>
       </c>
       <c r="J40" s="0">
-        <v>0.29262958497419689</v>
+        <v>3.0396260866258373</v>
       </c>
       <c r="K40" s="0">
         <v>2</v>
@@ -2082,28 +2082,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>495.67720000000003</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.207807476234215</v>
+        <v>21.273012910900665</v>
       </c>
       <c r="F41" s="0">
-        <v>0.70780747623421547</v>
+        <v>0.77301291090066471</v>
       </c>
       <c r="G41" s="0">
-        <v>0.70780747623421547</v>
+        <v>0.77301291090066471</v>
       </c>
       <c r="H41" s="0">
-        <v>20.707807476234215</v>
+        <v>20.773012910900665</v>
       </c>
       <c r="I41" s="0">
-        <v>0.20780747623421547</v>
+        <v>0.27301291090066471</v>
       </c>
       <c r="J41" s="0">
-        <v>0.20780747623421547</v>
+        <v>0.27301291090066471</v>
       </c>
       <c r="K41" s="0">
         <v>2</v>
@@ -2123,28 +2123,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>748.70209999999997</v>
+        <v>523.23350000000005</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.47900467441157</v>
+        <v>19.170024293901879</v>
       </c>
       <c r="F42" s="0">
-        <v>2.2290046744115699</v>
+        <v>-0.079975706098121435</v>
       </c>
       <c r="G42" s="0">
-        <v>2.2290046744115699</v>
+        <v>0.079975706098121435</v>
       </c>
       <c r="H42" s="0">
-        <v>20.97900467441157</v>
+        <v>18.670024293901879</v>
       </c>
       <c r="I42" s="0">
-        <v>1.7290046744115699</v>
+        <v>-0.57997570609812144</v>
       </c>
       <c r="J42" s="0">
-        <v>1.7290046744115699</v>
+        <v>0.57997570609812144</v>
       </c>
       <c r="K42" s="0">
         <v>4</v>
@@ -2164,28 +2164,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>494.75599999999997</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>21.332886012815894</v>
+        <v>19.639453877565202</v>
       </c>
       <c r="F43" s="0">
-        <v>1.3328860128158944</v>
+        <v>-0.36054612243479767</v>
       </c>
       <c r="G43" s="0">
-        <v>1.3328860128158944</v>
+        <v>0.36054612243479767</v>
       </c>
       <c r="H43" s="0">
-        <v>20.832886012815894</v>
+        <v>19.139453877565202</v>
       </c>
       <c r="I43" s="0">
-        <v>0.83288601281589436</v>
+        <v>-0.86054612243479767</v>
       </c>
       <c r="J43" s="0">
-        <v>0.83288601281589436</v>
+        <v>0.86054612243479767</v>
       </c>
       <c r="K43" s="0">
         <v>5</v>
@@ -2205,28 +2205,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>494.714</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.931319551441821</v>
+        <v>21.067957291586971</v>
       </c>
       <c r="F44" s="0">
-        <v>0.93131955144182044</v>
+        <v>1.0679572915869713</v>
       </c>
       <c r="G44" s="0">
-        <v>0.93131955144182044</v>
+        <v>1.0679572915869713</v>
       </c>
       <c r="H44" s="0">
-        <v>20.431319551441821</v>
+        <v>20.567957291586971</v>
       </c>
       <c r="I44" s="0">
-        <v>0.43131955144182044</v>
+        <v>0.56795729158697128</v>
       </c>
       <c r="J44" s="0">
-        <v>0.43131955144182044</v>
+        <v>0.56795729158697128</v>
       </c>
       <c r="K44" s="0">
         <v>3</v>
@@ -2246,28 +2246,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>497.33580000000001</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.255284986787213</v>
+        <v>19.820279792266362</v>
       </c>
       <c r="F45" s="0">
-        <v>1.2552849867872133</v>
+        <v>-0.17972020773363795</v>
       </c>
       <c r="G45" s="0">
-        <v>1.2552849867872133</v>
+        <v>0.17972020773363795</v>
       </c>
       <c r="H45" s="0">
-        <v>20.755284986787213</v>
+        <v>19.320279792266362</v>
       </c>
       <c r="I45" s="0">
-        <v>0.75528498678721334</v>
+        <v>-0.67972020773363795</v>
       </c>
       <c r="J45" s="0">
-        <v>0.75528498678721334</v>
+        <v>0.67972020773363795</v>
       </c>
       <c r="K45" s="0">
         <v>1</v>
@@ -2287,28 +2287,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>254.3287</v>
+        <v>725.4751</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.930608976856366</v>
+        <v>22.742651388633707</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.0693910231436341</v>
+        <v>0.74265138863370694</v>
       </c>
       <c r="G46" s="0">
-        <v>1.0693910231436341</v>
+        <v>0.74265138863370694</v>
       </c>
       <c r="H46" s="0">
-        <v>20.430608976856366</v>
+        <v>22.242651388633707</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.5693910231436341</v>
+        <v>0.24265138863370694</v>
       </c>
       <c r="J46" s="0">
-        <v>1.5693910231436341</v>
+        <v>0.24265138863370694</v>
       </c>
       <c r="K46" s="0">
         <v>3</v>
@@ -2328,28 +2328,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>247.4494</v>
+        <v>700.72990000000004</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.930588641805798</v>
+        <v>22.055238789784479</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.069411358194202</v>
+        <v>0.055238789784478826</v>
       </c>
       <c r="G47" s="0">
-        <v>1.069411358194202</v>
+        <v>0.055238789784478826</v>
       </c>
       <c r="H47" s="0">
-        <v>20.430588641805798</v>
+        <v>21.555238789784479</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.569411358194202</v>
+        <v>-0.44476121021552117</v>
       </c>
       <c r="J47" s="0">
-        <v>1.569411358194202</v>
+        <v>0.44476121021552117</v>
       </c>
       <c r="K47" s="0">
         <v>3</v>
@@ -2369,28 +2369,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>243.8894</v>
+        <v>697.40779999999995</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>20.556206644460474</v>
+        <v>21.679559503888815</v>
       </c>
       <c r="F48" s="0">
-        <v>-2.4437933555395261</v>
+        <v>-1.3204404961111855</v>
       </c>
       <c r="G48" s="0">
-        <v>2.4437933555395261</v>
+        <v>1.3204404961111855</v>
       </c>
       <c r="H48" s="0">
-        <v>20.056206644460474</v>
+        <v>21.179559503888815</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.9437933555395262</v>
+        <v>-1.8204404961111855</v>
       </c>
       <c r="J48" s="0">
-        <v>2.9437933555395262</v>
+        <v>1.8204404961111855</v>
       </c>
       <c r="K48" s="0">
         <v>1</v>
@@ -2410,28 +2410,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>246.52959999999999</v>
+        <v>664.56500000000005</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>20.571653301752171</v>
+        <v>20.865982691968274</v>
       </c>
       <c r="F49" s="0">
-        <v>-1.1783466982478288</v>
+        <v>-0.8840173080317264</v>
       </c>
       <c r="G49" s="0">
-        <v>1.1783466982478288</v>
+        <v>0.8840173080317264</v>
       </c>
       <c r="H49" s="0">
-        <v>20.071653301752171</v>
+        <v>20.365982691968274</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.6783466982478288</v>
+        <v>-1.3840173080317264</v>
       </c>
       <c r="J49" s="0">
-        <v>1.6783466982478288</v>
+        <v>1.3840173080317264</v>
       </c>
       <c r="K49" s="0">
         <v>1</v>
@@ -2451,28 +2451,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>253.74959999999999</v>
+        <v>689.15930000000003</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>20.876141253973771</v>
+        <v>21.516553999645911</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.62385874602622948</v>
+        <v>0.016553999645910977</v>
       </c>
       <c r="G50" s="0">
-        <v>0.62385874602622948</v>
+        <v>0.016553999645910977</v>
       </c>
       <c r="H50" s="0">
-        <v>20.376141253973771</v>
+        <v>21.016553999645911</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.1238587460262295</v>
+        <v>-0.48344600035408902</v>
       </c>
       <c r="J50" s="0">
-        <v>1.1238587460262295</v>
+        <v>0.48344600035408902</v>
       </c>
       <c r="K50" s="0">
         <v>5</v>
@@ -2492,28 +2492,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>245.00049999999999</v>
+        <v>610.64480000000003</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.207142401396876</v>
+        <v>20.058369902151345</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0071424013968766</v>
+        <v>0.85836990215134534</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0071424013968766</v>
+        <v>0.85836990215134534</v>
       </c>
       <c r="H51" s="0">
-        <v>20.707142401396876</v>
+        <v>19.558369902151345</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5071424013968766</v>
+        <v>0.35836990215134534</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5071424013968766</v>
+        <v>0.35836990215134534</v>
       </c>
       <c r="K51" s="0">
         <v>2</v>
@@ -2533,28 +2533,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>249.13220000000001</v>
+        <v>576.71630000000005</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>20.586801279238941</v>
+        <v>19.80262478566274</v>
       </c>
       <c r="F52" s="0">
-        <v>3.0868012792389408</v>
+        <v>2.30262478566274</v>
       </c>
       <c r="G52" s="0">
-        <v>3.0868012792389408</v>
+        <v>2.30262478566274</v>
       </c>
       <c r="H52" s="0">
-        <v>20.086801279238941</v>
+        <v>19.30262478566274</v>
       </c>
       <c r="I52" s="0">
-        <v>2.5868012792389408</v>
+        <v>1.80262478566274</v>
       </c>
       <c r="J52" s="0">
-        <v>2.5868012792389408</v>
+        <v>1.80262478566274</v>
       </c>
       <c r="K52" s="0">
         <v>1</v>
@@ -2574,28 +2574,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>248.1223</v>
+        <v>598.05470000000003</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>20.797349274481945</v>
+        <v>19.968049878729598</v>
       </c>
       <c r="F53" s="0">
-        <v>2.3973492744819467</v>
+        <v>1.5680498787295996</v>
       </c>
       <c r="G53" s="0">
-        <v>2.3973492744819467</v>
+        <v>1.5680498787295996</v>
       </c>
       <c r="H53" s="0">
-        <v>20.297349274481945</v>
+        <v>19.468049878729598</v>
       </c>
       <c r="I53" s="0">
-        <v>1.8973492744819467</v>
+        <v>1.0680498787295996</v>
       </c>
       <c r="J53" s="0">
-        <v>1.8973492744819467</v>
+        <v>1.0680498787295996</v>
       </c>
       <c r="K53" s="0">
         <v>4</v>
@@ -2615,28 +2615,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>246.3682</v>
+        <v>573.06939999999997</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.858168016756267</v>
+        <v>19.600302790129582</v>
       </c>
       <c r="F54" s="0">
-        <v>1.8581680167562666</v>
+        <v>0.60030279012958232</v>
       </c>
       <c r="G54" s="0">
-        <v>1.8581680167562666</v>
+        <v>0.60030279012958232</v>
       </c>
       <c r="H54" s="0">
-        <v>20.358168016756267</v>
+        <v>19.100302790129582</v>
       </c>
       <c r="I54" s="0">
-        <v>1.3581680167562666</v>
+        <v>0.10030279012958232</v>
       </c>
       <c r="J54" s="0">
-        <v>1.3581680167562666</v>
+        <v>0.10030279012958232</v>
       </c>
       <c r="K54" s="0">
         <v>5</v>
@@ -2656,28 +2656,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>503.7901</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.320629224325359</v>
+        <v>19.813604622050985</v>
       </c>
       <c r="F55" s="0">
-        <v>1.8206292243253586</v>
+        <v>0.31360462205098472</v>
       </c>
       <c r="G55" s="0">
-        <v>1.8206292243253586</v>
+        <v>0.31360462205098472</v>
       </c>
       <c r="H55" s="0">
-        <v>20.820629224325359</v>
+        <v>19.313604622050985</v>
       </c>
       <c r="I55" s="0">
-        <v>1.3206292243253586</v>
+        <v>-0.18639537794901529</v>
       </c>
       <c r="J55" s="0">
-        <v>1.3206292243253586</v>
+        <v>0.18639537794901529</v>
       </c>
       <c r="K55" s="0">
         <v>5</v>
@@ -2697,28 +2697,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>514.5693</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.931378243414798</v>
+        <v>22.063497730567878</v>
       </c>
       <c r="F56" s="0">
-        <v>0.43137824341479814</v>
+        <v>1.5634977305678781</v>
       </c>
       <c r="G56" s="0">
-        <v>0.43137824341479814</v>
+        <v>1.5634977305678781</v>
       </c>
       <c r="H56" s="0">
-        <v>20.431378243414798</v>
+        <v>21.563497730567878</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.068621756585201865</v>
+        <v>1.0634977305678781</v>
       </c>
       <c r="J56" s="0">
-        <v>0.068621756585201865</v>
+        <v>1.0634977305678781</v>
       </c>
       <c r="K56" s="0">
         <v>3</v>
@@ -2738,28 +2738,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>488.1463</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.259942023445888</v>
+        <v>20.55227348042953</v>
       </c>
       <c r="F57" s="0">
-        <v>0.25994202344588757</v>
+        <v>-0.44772651957046961</v>
       </c>
       <c r="G57" s="0">
-        <v>0.25994202344588757</v>
+        <v>0.44772651957046961</v>
       </c>
       <c r="H57" s="0">
-        <v>20.759942023445888</v>
+        <v>20.05227348042953</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.24005797655411243</v>
+        <v>-0.94772651957046961</v>
       </c>
       <c r="J57" s="0">
-        <v>0.24005797655411243</v>
+        <v>0.94772651957046961</v>
       </c>
       <c r="K57" s="0">
         <v>1</v>
@@ -2779,28 +2779,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>336.15499999999997</v>
+        <v>713.38980000000004</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>20.691768263620631</v>
+        <v>22.220901589190426</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.8082317363793692</v>
+        <v>-1.2790984108095742</v>
       </c>
       <c r="G58" s="0">
-        <v>2.8082317363793692</v>
+        <v>1.2790984108095742</v>
       </c>
       <c r="H58" s="0">
-        <v>20.191768263620631</v>
+        <v>21.720901589190426</v>
       </c>
       <c r="I58" s="0">
-        <v>-3.3082317363793692</v>
+        <v>-1.7790984108095742</v>
       </c>
       <c r="J58" s="0">
-        <v>3.3082317363793692</v>
+        <v>1.7790984108095742</v>
       </c>
       <c r="K58" s="0">
         <v>4</v>
@@ -2820,28 +2820,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>505.59070000000003</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.20783377947113</v>
+        <v>21.259346511125521</v>
       </c>
       <c r="F59" s="0">
-        <v>0.70783377947113024</v>
+        <v>0.75934651112552132</v>
       </c>
       <c r="G59" s="0">
-        <v>0.70783377947113024</v>
+        <v>0.75934651112552132</v>
       </c>
       <c r="H59" s="0">
-        <v>20.70783377947113</v>
+        <v>20.759346511125521</v>
       </c>
       <c r="I59" s="0">
-        <v>0.20783377947113024</v>
+        <v>0.25934651112552132</v>
       </c>
       <c r="J59" s="0">
-        <v>0.20783377947113024</v>
+        <v>0.25934651112552132</v>
       </c>
       <c r="K59" s="0">
         <v>2</v>
@@ -2861,28 +2861,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>473.07850000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>21.34973512825826</v>
+        <v>21.785222797158827</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.15026487174174008</v>
+        <v>0.28522279715882704</v>
       </c>
       <c r="G60" s="0">
-        <v>0.15026487174174008</v>
+        <v>0.28522279715882704</v>
       </c>
       <c r="H60" s="0">
-        <v>20.84973512825826</v>
+        <v>21.285222797158827</v>
       </c>
       <c r="I60" s="0">
-        <v>-0.65026487174174008</v>
+        <v>-0.21477720284117297</v>
       </c>
       <c r="J60" s="0">
-        <v>0.65026487174174008</v>
+        <v>0.21477720284117297</v>
       </c>
       <c r="K60" s="0">
         <v>5</v>
@@ -2902,28 +2902,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>495.04969999999997</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>21.10807190727979</v>
+        <v>20.810912180688522</v>
       </c>
       <c r="F61" s="0">
-        <v>1.1080719072797898</v>
+        <v>0.810912180688522</v>
       </c>
       <c r="G61" s="0">
-        <v>1.1080719072797898</v>
+        <v>0.810912180688522</v>
       </c>
       <c r="H61" s="0">
-        <v>20.60807190727979</v>
+        <v>20.310912180688522</v>
       </c>
       <c r="I61" s="0">
-        <v>0.60807190727978977</v>
+        <v>0.310912180688522</v>
       </c>
       <c r="J61" s="0">
-        <v>0.60807190727978977</v>
+        <v>0.310912180688522</v>
       </c>
       <c r="K61" s="0">
         <v>4</v>
@@ -2943,28 +2943,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>502.70080000000002</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.137661371959364</v>
+        <v>21.704768523539503</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.8623386280406358</v>
+        <v>-1.2952314764604971</v>
       </c>
       <c r="G62" s="0">
-        <v>1.8623386280406358</v>
+        <v>1.2952314764604971</v>
       </c>
       <c r="H62" s="0">
-        <v>20.637661371959364</v>
+        <v>21.204768523539503</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.3623386280406358</v>
+        <v>-1.7952314764604971</v>
       </c>
       <c r="J62" s="0">
-        <v>2.3623386280406358</v>
+        <v>1.7952314764604971</v>
       </c>
       <c r="K62" s="0">
         <v>4</v>
@@ -2984,28 +2984,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>497.99149999999997</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.931329239683016</v>
+        <v>21.37357006616736</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.5686707603169836</v>
+        <v>-0.12642993383263956</v>
       </c>
       <c r="G63" s="0">
-        <v>0.5686707603169836</v>
+        <v>0.12642993383263956</v>
       </c>
       <c r="H63" s="0">
-        <v>20.431329239683016</v>
+        <v>20.87357006616736</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.0686707603169836</v>
+        <v>-0.62642993383263956</v>
       </c>
       <c r="J63" s="0">
-        <v>1.0686707603169836</v>
+        <v>0.62642993383263956</v>
       </c>
       <c r="K63" s="0">
         <v>3</v>
@@ -3025,28 +3025,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>754.95579999999995</v>
+        <v>643.54809999999998</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>21.076344939701592</v>
+        <v>20.304937955636362</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.4236550602984082</v>
+        <v>-2.1950620443636382</v>
       </c>
       <c r="G64" s="0">
-        <v>1.4236550602984082</v>
+        <v>2.1950620443636382</v>
       </c>
       <c r="H64" s="0">
-        <v>20.576344939701592</v>
+        <v>19.804937955636362</v>
       </c>
       <c r="I64" s="0">
-        <v>-1.9236550602984082</v>
+        <v>-2.6950620443636382</v>
       </c>
       <c r="J64" s="0">
-        <v>1.9236550602984082</v>
+        <v>2.6950620443636382</v>
       </c>
       <c r="K64" s="0">
         <v>5</v>
@@ -3066,28 +3066,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>505.15969999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.207832635908417</v>
+        <v>19.905064671043469</v>
       </c>
       <c r="F65" s="0">
-        <v>1.9578326359084173</v>
+        <v>0.6550646710434691</v>
       </c>
       <c r="G65" s="0">
-        <v>1.9578326359084173</v>
+        <v>0.6550646710434691</v>
       </c>
       <c r="H65" s="0">
-        <v>20.707832635908417</v>
+        <v>19.405064671043469</v>
       </c>
       <c r="I65" s="0">
-        <v>1.4578326359084173</v>
+        <v>0.15506467104346911</v>
       </c>
       <c r="J65" s="0">
-        <v>1.4578326359084173</v>
+        <v>0.15506467104346911</v>
       </c>
       <c r="K65" s="0">
         <v>2</v>
@@ -3107,28 +3107,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>492.4178</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.257964362458182</v>
+        <v>22.05831600238259</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.242035637541818</v>
+        <v>-1.4416839976174103</v>
       </c>
       <c r="G66" s="0">
-        <v>2.242035637541818</v>
+        <v>1.4416839976174103</v>
       </c>
       <c r="H66" s="0">
-        <v>20.757964362458182</v>
+        <v>21.55831600238259</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.742035637541818</v>
+        <v>-1.9416839976174103</v>
       </c>
       <c r="J66" s="0">
-        <v>2.742035637541818</v>
+        <v>1.9416839976174103</v>
       </c>
       <c r="K66" s="0">
         <v>1</v>
@@ -3148,28 +3148,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>504.11689999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.25092775343856</v>
+        <v>20.40919578501758</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.24907224656143967</v>
+        <v>-1.0908042149824198</v>
       </c>
       <c r="G67" s="0">
-        <v>0.24907224656143967</v>
+        <v>1.0908042149824198</v>
       </c>
       <c r="H67" s="0">
-        <v>20.75092775343856</v>
+        <v>19.90919578501758</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.74907224656143967</v>
+        <v>-1.5908042149824198</v>
       </c>
       <c r="J67" s="0">
-        <v>0.74907224656143967</v>
+        <v>1.5908042149824198</v>
       </c>
       <c r="K67" s="0">
         <v>1</v>
@@ -3189,28 +3189,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>320.78059999999999</v>
+        <v>581.15859999999998</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>20.956401923106888</v>
+        <v>19.828512518237506</v>
       </c>
       <c r="F68" s="0">
-        <v>1.9564019231068883</v>
+        <v>0.82851251823750616</v>
       </c>
       <c r="G68" s="0">
-        <v>1.9564019231068883</v>
+        <v>0.82851251823750616</v>
       </c>
       <c r="H68" s="0">
-        <v>20.456401923106888</v>
+        <v>19.328512518237506</v>
       </c>
       <c r="I68" s="0">
-        <v>1.4564019231068883</v>
+        <v>0.32851251823750616</v>
       </c>
       <c r="J68" s="0">
-        <v>1.4564019231068883</v>
+        <v>0.32851251823750616</v>
       </c>
       <c r="K68" s="0">
         <v>1</v>
@@ -3268,19 +3268,19 @@
         <v>84</v>
       </c>
       <c r="B2" s="0">
-        <v>1.4870000000000001</v>
+        <v>1.0880000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8180000000000001</v>
+        <v>1.357</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.105</v>
+        <v>0.65000000000000002</v>
       </c>
       <c r="E2" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F2" s="0">
-        <v>0.02</v>
+        <v>-0.0060000000000000001</v>
       </c>
       <c r="G2" s="0"/>
     </row>
@@ -3289,22 +3289,22 @@
         <v>85</v>
       </c>
       <c r="B3" s="0">
-        <v>0.025000000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="C3" s="0">
-        <v>0.027</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>0.088999999999999996</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="F3" s="0">
-        <v>0.043999999999999998</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="G3" s="0">
-        <v>2.1000000000000001</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3323,22 +3323,22 @@
         <v>87</v>
       </c>
       <c r="B5" s="0">
-        <v>1.4930000000000001</v>
+        <v>1.127</v>
       </c>
       <c r="C5" s="0">
-        <v>1.8799999999999999</v>
+        <v>1.448</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.105</v>
+        <v>0.65000000000000002</v>
       </c>
       <c r="E5" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.47999999999999998</v>
+        <v>-0.50600000000000001</v>
       </c>
       <c r="G5" s="0">
-        <v>39.399999999999999</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -3346,19 +3346,19 @@
         <v>88</v>
       </c>
       <c r="B6" s="0">
-        <v>1.466</v>
+        <v>1.105</v>
       </c>
       <c r="C6" s="0">
-        <v>1.8049999999999999</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.045999999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>0.002</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="F6" s="0">
-        <v>0.0050000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="G6" s="0"/>
     </row>
@@ -3367,22 +3367,22 @@
         <v>89</v>
       </c>
       <c r="B7" s="0">
-        <v>1.482</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>1.871</v>
+        <v>1.456</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.045999999999999999</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="E7" s="0">
-        <v>0.002</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.495</v>
+        <v>-0.48599999999999999</v>
       </c>
       <c r="G7" s="0">
-        <v>38.799999999999997</v>
+        <v>50.700000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -3470,9 +3470,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.7109375" customWidth="true"/>
+    <col min="2" max="2" width="6.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.7109375" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
     <col min="5" max="5" width="4.5703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3498,13 +3498,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>20.348600000000001</v>
+        <v>8.7514000000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>0.74609999999999999</v>
+        <v>1.6551</v>
       </c>
       <c r="D2" s="0">
-        <v>27.271999999999999</v>
+        <v>5.2880000000000003</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3515,16 +3515,16 @@
         <v>113</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0014</v>
+        <v>0.0189</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0015</v>
+        <v>0.0025000000000000001</v>
       </c>
       <c r="D3" s="0">
-        <v>0.89500000000000002</v>
+        <v>7.4279999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.37430000000000002</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
